--- a/education_forms/027_lecture_evaluation_form_template--education_forms.xlsx
+++ b/education_forms/027_lecture_evaluation_form_template--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>what_was_the_overall_quality_of_the_lecture</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Overall Quality of the Lecture</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please provide a brief overview of your experience.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -543,18 +547,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>overall_rating</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>overall_rating</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Overall Rating</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Rate the overall quality of the lecture.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,10 +579,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>provide_feedback</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Feedback</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please provide any comments or suggestions.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -594,13 +606,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lecturer_name</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Lecturer's Name</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please provide the lecturer's name.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +628,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>date_of_lecture</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>date_of_lecture</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Date of the Lecture</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please provide the date of the lecture.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +655,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>time_of_lecture</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>time_of_lecture</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Time of the Lecture</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please provide the time of the lecture.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +682,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>helpfulness</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>what_was_covered</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>How Helpful?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>How helpful was the content?</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +709,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>engagement</t>
+          <t>relevance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>engagement</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Relevance</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>How relevant was the content?</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,18 +736,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>helpfulness</t>
+          <t>enjoyment</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>helpfulness</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Enjoyment</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>How enjoyable was the lecture?</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +763,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>relevance</t>
+          <t>pace</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>relevance</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Pace</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>How well-paced was the lecture?</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,18 +790,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>enjoyment</t>
+          <t>overall_satisfaction</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>enjoyment</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Overall Satisfaction</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Rate your overall satisfaction.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,41 +817,49 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>clarity</t>
+          <t>would_recommend</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>clarity</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Would Recommend</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Would you recommend this lecture?</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>pace</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>pace</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please provide any additional comments or suggestions.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,478 +871,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>presentation</t>
+          <t>would_recommend_lecture_to</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>presentation</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Would Recommend to Others</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Would you recommend this lecture to others?</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>overall_quality</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>overall_quality</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>prophets</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>prophets</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>uto</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>uto</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>utoo</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>utoo</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>u_prophets</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>u_prophets</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>utoooo</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>utoooo</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>utop</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>utop</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>utoop</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>utoop</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>overall_satisfaction</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>overall_satisfaction</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>would_recommend</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>would_recommend</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>would_recommend_lecture</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>would_recommend_lecture</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>would_recommend_lecture_to</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>would_recommend_lecture_to</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>would_recommend_lecture_to_another</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>would_recommend_lecture_to_another</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>uto</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>uto</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>utoo</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>utoo</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>utoooo</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>utoooo</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>utop</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>utop</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>utoop</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>utoop</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1308,7 +904,7 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1333,7 +929,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>rating_choices</t>
+          <t>overall_rating_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1350,7 +946,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>rating_choices</t>
+          <t>overall_rating_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1367,7 +963,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>rating_choices</t>
+          <t>overall_rating_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1384,7 +980,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>rating_choices</t>
+          <t>overall_rating_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
